--- a/data/trans_bre/IP11-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP11-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,5; 5,93</t>
+          <t>-13,39; 5,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,24; -2,5</t>
+          <t>-15,02; -2,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,83; 2,15</t>
+          <t>-12,96; 1,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 5,56</t>
+          <t>-8,27; 5,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-78,12; 88,47</t>
+          <t>-76,28; 82,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; inf</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-89,52; 73,86</t>
+          <t>-91,08; 89,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 4,1</t>
+          <t>-1,88; 4,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 5,99</t>
+          <t>-6,3; 6,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 4,35</t>
+          <t>-6,35; 3,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 2,47</t>
+          <t>-6,32; 2,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,24 +785,24 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-51,2; 100,61</t>
+          <t>-51,35; 118,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-70,53; 141,51</t>
+          <t>-71,96; 116,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-89,36; 186,84</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,32 +860,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 7,06</t>
+          <t>-7,94; 6,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,01; 7,61</t>
+          <t>-12,86; 8,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 2,3</t>
+          <t>-5,1; 2,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 5,92</t>
+          <t>-4,17; 5,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-65,45; 133,27</t>
+          <t>-66,28; 137,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-55,63; 54,32</t>
+          <t>-52,41; 61,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -960,37 +960,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 6,8</t>
+          <t>-8,14; 6,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 3,43</t>
+          <t>-8,77; 3,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,95; 3,45</t>
+          <t>-9,89; 4,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 2,15</t>
+          <t>-7,52; 2,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-63,11; 120,61</t>
+          <t>-58,77; 110,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-92,11; 251,26</t>
+          <t>-89,64; 246,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-76,86; 76,34</t>
+          <t>-75,52; 82,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,69; 15,02</t>
+          <t>1,7; 14,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 7,99</t>
+          <t>-6,62; 8,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 1,49</t>
+          <t>-7,32; 2,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 0,0</t>
+          <t>-7,85; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,49 +1160,49 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 2,75</t>
+          <t>-8,87; 2,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-20,83; 3,82</t>
+          <t>-19,7; 4,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-12,38; 5,29</t>
+          <t>-13,1; 4,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 11,03</t>
+          <t>-3,51; 11,66</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 290,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-68,54; 32,21</t>
+          <t>-70,12; 36,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-83,06; 128,58</t>
+          <t>-88,93; 139,47</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-85,83; 959,56</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 1,44</t>
+          <t>-8,43; 1,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,53; 0,77</t>
+          <t>-11,88; 0,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 2,53</t>
+          <t>-3,87; 2,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 2,48</t>
+          <t>-4,96; 2,66</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-73,85; 31,31</t>
+          <t>-73,38; 39,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-66,07; 8,85</t>
+          <t>-68,51; 7,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-83,67; 279,8</t>
+          <t>-86,31; 210,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-78,22; 109,58</t>
+          <t>-73,05; 120,74</t>
         </is>
       </c>
     </row>
@@ -1360,37 +1360,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 1,48</t>
+          <t>-5,51; 1,29</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 3,89</t>
+          <t>-1,71; 4,06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 0,34</t>
+          <t>-5,62; 0,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 1,9</t>
+          <t>-1,19; 1,86</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-77,18; 58,4</t>
+          <t>-78,66; 51,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-53,75; 356,01</t>
+          <t>-54,41; 399,03</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-86,08; 35,59</t>
+          <t>-86,12; 34,53</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 0,81</t>
+          <t>-3,28; 0,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,91; -0,17</t>
+          <t>-4,86; -0,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,94; -0,26</t>
+          <t>-3,93; -0,35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 1,03</t>
+          <t>-2,37; 0,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-42,98; 16,24</t>
+          <t>-43,8; 14,68</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-44,13; -1,12</t>
+          <t>-44,18; -1,99</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-60,09; -5,16</t>
+          <t>-59,28; -6,11</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-51,01; 46,13</t>
+          <t>-56,89; 36,86</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP11-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP11-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,39; 5,63</t>
+          <t>-12,4; 6,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,02; -2,35</t>
+          <t>-14,52; -2,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 1,78</t>
+          <t>-14,2; 1,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 5,76</t>
+          <t>-8,33; 5,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-76,28; 82,84</t>
+          <t>-73,79; 104,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 0,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-91,08; 89,68</t>
+          <t>-91,98; 54,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-99,88; —</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,75</t>
+          <t>-1,74</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-43,36%</t>
+          <t>-42,99%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 4,16</t>
+          <t>-1,36; 4,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 6,34</t>
+          <t>-6,72; 6,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 3,82</t>
+          <t>-6,0; 4,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 2,22</t>
+          <t>-6,42; 1,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,17 +785,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-51,35; 118,37</t>
+          <t>-52,52; 117,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-71,96; 116,18</t>
+          <t>-68,22; 166,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-90,54; 145,17</t>
         </is>
       </c>
     </row>
@@ -860,32 +860,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 6,78</t>
+          <t>-7,55; 7,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 8,06</t>
+          <t>-13,5; 8,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 2,32</t>
+          <t>-5,1; 2,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 5,37</t>
+          <t>-4,44; 5,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-66,28; 137,11</t>
+          <t>-64,82; 146,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-52,41; 61,44</t>
+          <t>-56,68; 71,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -960,37 +960,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 6,62</t>
+          <t>-7,97; 6,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 3,43</t>
+          <t>-8,73; 2,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 4,09</t>
+          <t>-10,82; 4,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 2,7</t>
+          <t>-7,91; 2,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-58,77; 110,13</t>
+          <t>-59,6; 119,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-89,64; 246,5</t>
+          <t>-90,37; 240,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-75,52; 82,53</t>
+          <t>-76,19; 88,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,7; 14,59</t>
+          <t>1,72; 15,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 8,2</t>
+          <t>-5,6; 8,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 2,75</t>
+          <t>-7,41; 2,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 0,0</t>
+          <t>-8,28; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1160,37 +1160,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 2,18</t>
+          <t>-8,51; 2,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-19,7; 4,02</t>
+          <t>-19,94; 3,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 4,62</t>
+          <t>-12,83; 4,3</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 11,66</t>
+          <t>-2,75; 12,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 189,27</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-70,12; 36,06</t>
+          <t>-69,88; 23,93</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-88,93; 139,47</t>
+          <t>-85,83; 92,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 1,88</t>
+          <t>-8,45; 1,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,88; 0,62</t>
+          <t>-11,25; 0,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 2,1</t>
+          <t>-3,69; 2,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 2,66</t>
+          <t>-5,17; 2,61</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-73,38; 39,31</t>
+          <t>-73,68; 36,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-68,51; 7,62</t>
+          <t>-64,51; 6,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-86,31; 210,97</t>
+          <t>-88,22; 249,4</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-73,05; 120,74</t>
+          <t>-76,93; 122,27</t>
         </is>
       </c>
     </row>
@@ -1360,37 +1360,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 1,29</t>
+          <t>-5,79; 1,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 4,06</t>
+          <t>-1,78; 4,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 0,42</t>
+          <t>-5,36; 0,59</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 1,86</t>
+          <t>-1,64; 1,89</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-78,66; 51,8</t>
+          <t>-81,37; 41,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-54,41; 399,03</t>
+          <t>-54,54; 367,79</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-86,12; 34,53</t>
+          <t>-84,02; 44,92</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-18,44%</t>
+          <t>-18,34%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 0,79</t>
+          <t>-3,21; 0,85</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,86; -0,17</t>
+          <t>-5,08; -0,34</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,93; -0,35</t>
+          <t>-3,85; -0,35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 0,88</t>
+          <t>-2,2; 0,98</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-43,8; 14,68</t>
+          <t>-43,46; 16,85</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-44,18; -1,99</t>
+          <t>-44,58; -2,96</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-59,28; -6,11</t>
+          <t>-60,74; -7,4</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-56,89; 36,86</t>
+          <t>-55,57; 44,5</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP11-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP11-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,5</t>
+          <t>0,58</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-10,45%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 6,47</t>
+          <t>-14,5; 5,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,52; -2,21</t>
+          <t>-15,24; -2,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,2; 1,6</t>
+          <t>-13,83; 2,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 5,68</t>
+          <t>-7,13; 7,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-73,79; 104,96</t>
+          <t>-78,12; 88,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,44</t>
+          <t>-100,0; inf</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-91,98; 54,15</t>
+          <t>-89,52; 73,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-99,88; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,74</t>
+          <t>-0,99</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-42,99%</t>
+          <t>-23,85%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 4,49</t>
+          <t>-1,36; 4,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 6,73</t>
+          <t>-6,38; 5,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 4,68</t>
+          <t>-6,2; 4,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 1,94</t>
+          <t>-5,68; 3,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,17 +785,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-52,52; 117,27</t>
+          <t>-51,2; 100,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-68,22; 166,72</t>
+          <t>-70,53; 141,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-90,54; 145,17</t>
+          <t>-90,48; 203,53</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,29</t>
+          <t>0,31</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,96%</t>
         </is>
       </c>
     </row>
@@ -860,32 +860,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 7,92</t>
+          <t>-8,23; 7,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,5; 8,9</t>
+          <t>-13,01; 7,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 2,33</t>
+          <t>-5,2; 2,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 5,67</t>
+          <t>-3,63; 5,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-64,82; 146,73</t>
+          <t>-65,45; 133,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-56,68; 71,25</t>
+          <t>-55,63; 54,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,27</t>
+          <t>-1,26</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-48,53%</t>
+          <t>-45,86%</t>
         </is>
       </c>
     </row>
@@ -960,37 +960,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 6,5</t>
+          <t>-9,1; 6,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 2,96</t>
+          <t>-9,5; 3,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,82; 4,09</t>
+          <t>-10,95; 3,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 2,55</t>
+          <t>-8,7; 2,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-59,6; 119,71</t>
+          <t>-63,11; 120,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-90,37; 240,52</t>
+          <t>-92,11; 251,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-76,19; 88,37</t>
+          <t>-76,86; 76,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-2,56</t>
+          <t>-2,74</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,72; 15,22</t>
+          <t>1,69; 15,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 8,17</t>
+          <t>-5,66; 7,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 2,71</t>
+          <t>-7,25; 1,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 0,0</t>
+          <t>-9,03; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3,37</t>
+          <t>3,44</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>85,99%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 2,65</t>
+          <t>-8,71; 2,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-19,94; 3,82</t>
+          <t>-20,83; 3,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-12,83; 4,3</t>
+          <t>-12,38; 5,29</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 12,05</t>
+          <t>-3,46; 10,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 189,27</t>
+          <t>-100,0; 290,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-69,88; 23,93</t>
+          <t>-68,54; 32,21</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-85,83; 92,01</t>
+          <t>-83,06; 128,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-89,7; 1008,97</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,17</t>
+          <t>-1,65</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-26,63%</t>
+          <t>-33,99%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 1,76</t>
+          <t>-8,54; 1,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,25; 0,6</t>
+          <t>-11,53; 0,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 2,2</t>
+          <t>-3,25; 2,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 2,61</t>
+          <t>-6,28; 2,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-73,68; 36,62</t>
+          <t>-73,85; 31,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-64,51; 6,98</t>
+          <t>-66,07; 8,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-88,22; 249,4</t>
+          <t>-83,67; 279,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-76,93; 122,27</t>
+          <t>-81,01; 99,8</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -1360,37 +1360,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 1,22</t>
+          <t>-5,86; 1,48</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 4,0</t>
+          <t>-1,51; 3,89</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 0,59</t>
+          <t>-5,51; 0,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 1,89</t>
+          <t>-1,2; 2,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-81,37; 41,1</t>
+          <t>-77,18; 58,4</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-54,54; 367,79</t>
+          <t>-53,75; 356,01</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-84,02; 44,92</t>
+          <t>-86,08; 35,59</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0,58</t>
+          <t>-0,45</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-18,34%</t>
+          <t>-14,0%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 0,85</t>
+          <t>-3,12; 0,81</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,08; -0,34</t>
+          <t>-4,91; -0,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,85; -0,35</t>
+          <t>-3,94; -0,26</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 0,98</t>
+          <t>-2,09; 1,16</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-43,46; 16,85</t>
+          <t>-42,98; 16,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-44,58; -2,96</t>
+          <t>-44,13; -1,12</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-60,74; -7,4</t>
+          <t>-60,09; -5,16</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-55,57; 44,5</t>
+          <t>-50,96; 51,94</t>
         </is>
       </c>
     </row>
